--- a/RQ.COR.111 - 10 - RQ.COR.111.xlsx
+++ b/RQ.COR.111 - 10 - RQ.COR.111.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Junior.antonio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BC0085-4A0C-41E6-BDE3-F94A5D033B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19359B8C-1DEA-4744-BF8E-15920707CA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="26">
   <si>
     <t>Limite mínimo aceitável</t>
   </si>
@@ -119,6 +119,9 @@
 </t>
   </si>
   <si>
+    <t>Monitores de triagem</t>
+  </si>
+  <si>
     <t>Família de Equipamentos:
 Esteira ergométrica</t>
   </si>
@@ -139,6 +142,9 @@
   </si>
   <si>
     <t>Cardioversores e Desfibrilador Automático (DEA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monitores </t>
   </si>
 </sst>
 </file>
@@ -1300,10 +1306,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="74" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" s="74" t="s">
-        <v>20</v>
       </c>
       <c r="C1" s="75" t="s">
         <v>2</v>
@@ -1317,7 +1323,7 @@
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="78">
         <v>20</v>
@@ -1336,7 +1342,7 @@
     </row>
     <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="78">
         <v>40</v>
@@ -1355,7 +1361,7 @@
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="72">
         <v>60</v>
@@ -1374,7 +1380,7 @@
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="78">
         <v>80</v>
@@ -1393,7 +1399,7 @@
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="79">
         <v>100</v>
@@ -1507,7 +1513,7 @@
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="80">
         <v>10</v>
@@ -1524,7 +1530,7 @@
     </row>
     <row r="13" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="81">
         <v>50</v>
@@ -1541,7 +1547,7 @@
     </row>
     <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="72">
         <v>100</v>
@@ -1563,7 +1569,7 @@
       <c r="B15" s="72">
         <v>20</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="80">
         <v>0.3</v>
       </c>
       <c r="D15" s="71">
@@ -1580,7 +1586,7 @@
       <c r="B16" s="72">
         <v>40</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="80">
         <v>0.3</v>
       </c>
       <c r="D16" s="71">
@@ -1660,7 +1666,7 @@
     </row>
     <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" s="72">
         <v>70</v>
@@ -1677,7 +1683,7 @@
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" s="72">
         <v>83</v>
@@ -1694,7 +1700,7 @@
     </row>
     <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" s="73">
         <v>97</v>
@@ -1711,7 +1717,7 @@
     </row>
     <row r="24" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="73">
         <v>30</v>
@@ -1728,7 +1734,7 @@
     </row>
     <row r="25" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="83">
         <v>100</v>
@@ -1745,7 +1751,7 @@
     </row>
     <row r="26" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" s="83">
         <v>240</v>
@@ -1762,7 +1768,7 @@
     </row>
     <row r="27" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" s="83">
         <v>60</v>
@@ -1779,7 +1785,7 @@
     </row>
     <row r="28" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B28" s="83">
         <v>120</v>
@@ -1796,7 +1802,7 @@
     </row>
     <row r="29" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B29" s="83">
         <v>200</v>
@@ -1813,7 +1819,7 @@
     </row>
     <row r="30" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" s="83">
         <v>30</v>
@@ -1830,7 +1836,7 @@
     </row>
     <row r="31" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B31" s="83">
         <v>80</v>
@@ -1847,7 +1853,7 @@
     </row>
     <row r="32" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B32" s="83">
         <v>150</v>
@@ -1864,7 +1870,7 @@
     </row>
     <row r="33" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B33" s="83">
         <v>15</v>
@@ -1881,7 +1887,7 @@
     </row>
     <row r="34" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34" s="83">
         <v>20</v>
@@ -1898,7 +1904,7 @@
     </row>
     <row r="35" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" s="83">
         <v>30</v>
@@ -1915,7 +1921,7 @@
     </row>
     <row r="36" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B36" s="83">
         <v>30</v>
@@ -1932,7 +1938,7 @@
     </row>
     <row r="37" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B37" s="83">
         <v>50</v>
@@ -1949,7 +1955,7 @@
     </row>
     <row r="38" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B38" s="83">
         <v>100</v>
@@ -1966,7 +1972,7 @@
     </row>
     <row r="39" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B39" s="83">
         <v>150</v>
@@ -1983,7 +1989,7 @@
     </row>
     <row r="40" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B40" s="83">
         <v>200</v>
@@ -2000,7 +2006,7 @@
     </row>
     <row r="41" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B41" s="83">
         <v>50</v>
@@ -2017,7 +2023,7 @@
     </row>
     <row r="42" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B42" s="83">
         <v>70</v>
@@ -2034,7 +2040,7 @@
     </row>
     <row r="43" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B43" s="83">
         <v>85</v>
@@ -2051,7 +2057,7 @@
     </row>
     <row r="44" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B44" s="83">
         <v>120</v>
@@ -2068,7 +2074,7 @@
     </row>
     <row r="45" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B45" s="83">
         <v>150</v>
@@ -2085,7 +2091,7 @@
     </row>
     <row r="46" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B46" s="83">
         <v>200</v>
@@ -2102,7 +2108,7 @@
     </row>
     <row r="47" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B47" s="83">
         <v>50</v>
@@ -2119,7 +2125,7 @@
     </row>
     <row r="48" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B48" s="83">
         <v>70</v>
@@ -2136,7 +2142,7 @@
     </row>
     <row r="49" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B49" s="83">
         <v>100</v>
@@ -2153,7 +2159,7 @@
     </row>
     <row r="50" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B50" s="83">
         <v>200</v>
@@ -2170,7 +2176,7 @@
     </row>
     <row r="51" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B51" s="83">
         <v>50</v>
@@ -2187,7 +2193,7 @@
     </row>
     <row r="52" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B52" s="83">
         <v>150</v>
@@ -2204,7 +2210,7 @@
     </row>
     <row r="53" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B53" s="83">
         <v>50</v>
@@ -2221,7 +2227,7 @@
     </row>
     <row r="54" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B54" s="83">
         <v>150</v>
@@ -2238,7 +2244,7 @@
     </row>
     <row r="55" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B55" s="83">
         <v>200</v>
@@ -2271,214 +2277,514 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="83"/>
-      <c r="B57" s="83"/>
-      <c r="C57" s="83"/>
-      <c r="D57" s="83"/>
-      <c r="E57" s="83"/>
+      <c r="A57" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="83">
+        <v>70</v>
+      </c>
+      <c r="C57" s="83">
+        <v>0.03</v>
+      </c>
+      <c r="D57" s="83">
+        <v>67.899999999999991</v>
+      </c>
+      <c r="E57" s="83">
+        <v>72.100000000000009</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="83"/>
-      <c r="B58" s="83"/>
-      <c r="C58" s="83"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="83"/>
+      <c r="A58" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" s="83">
+        <v>83</v>
+      </c>
+      <c r="C58" s="83">
+        <v>0.03</v>
+      </c>
+      <c r="D58" s="83">
+        <v>80.509999999999991</v>
+      </c>
+      <c r="E58" s="83">
+        <v>85.49</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="83"/>
-      <c r="B59" s="83"/>
-      <c r="C59" s="83"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="83"/>
+      <c r="A59" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="83">
+        <v>97</v>
+      </c>
+      <c r="C59" s="83">
+        <v>0.03</v>
+      </c>
+      <c r="D59" s="83">
+        <v>94.09</v>
+      </c>
+      <c r="E59" s="83">
+        <v>99.91</v>
+      </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="83"/>
-      <c r="B60" s="83"/>
-      <c r="C60" s="83"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="83"/>
+      <c r="A60" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" s="83">
+        <v>30</v>
+      </c>
+      <c r="C60" s="83">
+        <v>5</v>
+      </c>
+      <c r="D60" s="83">
+        <v>25</v>
+      </c>
+      <c r="E60" s="83">
+        <v>35</v>
+      </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="83"/>
-      <c r="B61" s="83"/>
-      <c r="C61" s="83"/>
-      <c r="D61" s="83"/>
-      <c r="E61" s="83"/>
+      <c r="A61" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" s="83">
+        <v>100</v>
+      </c>
+      <c r="C61" s="83">
+        <v>5</v>
+      </c>
+      <c r="D61" s="83">
+        <v>95</v>
+      </c>
+      <c r="E61" s="83">
+        <v>105</v>
+      </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="83"/>
-      <c r="B62" s="83"/>
-      <c r="C62" s="83"/>
-      <c r="D62" s="83"/>
-      <c r="E62" s="83"/>
+      <c r="A62" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" s="83">
+        <v>240</v>
+      </c>
+      <c r="C62" s="83">
+        <v>5</v>
+      </c>
+      <c r="D62" s="83">
+        <v>235</v>
+      </c>
+      <c r="E62" s="83">
+        <v>245</v>
+      </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="83"/>
-      <c r="B63" s="83"/>
-      <c r="C63" s="83"/>
-      <c r="D63" s="83"/>
-      <c r="E63" s="83"/>
+      <c r="A63" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" s="83">
+        <v>60</v>
+      </c>
+      <c r="C63" s="83">
+        <v>5</v>
+      </c>
+      <c r="D63" s="83">
+        <v>55</v>
+      </c>
+      <c r="E63" s="83">
+        <v>65</v>
+      </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="83"/>
-      <c r="B64" s="83"/>
-      <c r="C64" s="83"/>
-      <c r="D64" s="83"/>
-      <c r="E64" s="83"/>
+      <c r="A64" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" s="83">
+        <v>120</v>
+      </c>
+      <c r="C64" s="83">
+        <v>5</v>
+      </c>
+      <c r="D64" s="83">
+        <v>115</v>
+      </c>
+      <c r="E64" s="83">
+        <v>125</v>
+      </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="83"/>
-      <c r="B65" s="83"/>
-      <c r="C65" s="83"/>
-      <c r="D65" s="83"/>
-      <c r="E65" s="83"/>
+      <c r="A65" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" s="83">
+        <v>200</v>
+      </c>
+      <c r="C65" s="83">
+        <v>5</v>
+      </c>
+      <c r="D65" s="83">
+        <v>195</v>
+      </c>
+      <c r="E65" s="83">
+        <v>205</v>
+      </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="83"/>
-      <c r="B66" s="83"/>
-      <c r="C66" s="83"/>
-      <c r="D66" s="83"/>
-      <c r="E66" s="83"/>
+      <c r="A66" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" s="83">
+        <v>30</v>
+      </c>
+      <c r="C66" s="83">
+        <v>5</v>
+      </c>
+      <c r="D66" s="83">
+        <v>25</v>
+      </c>
+      <c r="E66" s="83">
+        <v>35</v>
+      </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="83"/>
-      <c r="B67" s="83"/>
-      <c r="C67" s="83"/>
-      <c r="D67" s="83"/>
-      <c r="E67" s="83"/>
+      <c r="A67" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" s="83">
+        <v>80</v>
+      </c>
+      <c r="C67" s="83">
+        <v>5</v>
+      </c>
+      <c r="D67" s="83">
+        <v>75</v>
+      </c>
+      <c r="E67" s="83">
+        <v>85</v>
+      </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="83"/>
-      <c r="B68" s="83"/>
-      <c r="C68" s="83"/>
-      <c r="D68" s="83"/>
-      <c r="E68" s="83"/>
+      <c r="A68" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" s="83">
+        <v>150</v>
+      </c>
+      <c r="C68" s="83">
+        <v>5</v>
+      </c>
+      <c r="D68" s="83">
+        <v>145</v>
+      </c>
+      <c r="E68" s="83">
+        <v>155</v>
+      </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="83"/>
-      <c r="B69" s="83"/>
-      <c r="C69" s="83"/>
-      <c r="D69" s="83"/>
-      <c r="E69" s="83"/>
+      <c r="A69" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" s="83">
+        <v>15</v>
+      </c>
+      <c r="C69" s="83">
+        <v>3</v>
+      </c>
+      <c r="D69" s="83">
+        <v>12</v>
+      </c>
+      <c r="E69" s="83">
+        <v>18</v>
+      </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="83"/>
-      <c r="B70" s="83"/>
-      <c r="C70" s="83"/>
-      <c r="D70" s="83"/>
-      <c r="E70" s="83"/>
+      <c r="A70" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" s="83">
+        <v>20</v>
+      </c>
+      <c r="C70" s="83">
+        <v>3</v>
+      </c>
+      <c r="D70" s="83">
+        <v>17</v>
+      </c>
+      <c r="E70" s="83">
+        <v>23</v>
+      </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="83"/>
-      <c r="B71" s="83"/>
-      <c r="C71" s="83"/>
-      <c r="D71" s="83"/>
-      <c r="E71" s="83"/>
+      <c r="A71" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" s="83">
+        <v>30</v>
+      </c>
+      <c r="C71" s="83">
+        <v>3</v>
+      </c>
+      <c r="D71" s="83">
+        <v>27</v>
+      </c>
+      <c r="E71" s="83">
+        <v>33</v>
+      </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="83"/>
-      <c r="B72" s="83"/>
-      <c r="C72" s="83"/>
-      <c r="D72" s="83"/>
-      <c r="E72" s="83"/>
+      <c r="A72" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B72" s="83">
+        <v>70</v>
+      </c>
+      <c r="C72" s="83">
+        <v>0.03</v>
+      </c>
+      <c r="D72" s="83">
+        <v>67.899999999999991</v>
+      </c>
+      <c r="E72" s="83">
+        <v>72.100000000000009</v>
+      </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="83"/>
-      <c r="B73" s="83"/>
-      <c r="C73" s="83"/>
-      <c r="D73" s="83"/>
-      <c r="E73" s="83"/>
+      <c r="A73" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" s="83">
+        <v>83</v>
+      </c>
+      <c r="C73" s="83">
+        <v>0.03</v>
+      </c>
+      <c r="D73" s="83">
+        <v>80.509999999999991</v>
+      </c>
+      <c r="E73" s="83">
+        <v>85.49</v>
+      </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="83"/>
-      <c r="B74" s="83"/>
-      <c r="C74" s="83"/>
-      <c r="D74" s="83"/>
-      <c r="E74" s="83"/>
+      <c r="A74" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B74" s="83">
+        <v>97</v>
+      </c>
+      <c r="C74" s="83">
+        <v>0.03</v>
+      </c>
+      <c r="D74" s="83">
+        <v>94.09</v>
+      </c>
+      <c r="E74" s="83">
+        <v>99.91</v>
+      </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="83"/>
-      <c r="B75" s="83"/>
-      <c r="C75" s="83"/>
-      <c r="D75" s="83"/>
-      <c r="E75" s="83"/>
+      <c r="A75" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B75" s="83">
+        <v>30</v>
+      </c>
+      <c r="C75" s="83">
+        <v>5</v>
+      </c>
+      <c r="D75" s="83">
+        <v>25</v>
+      </c>
+      <c r="E75" s="83">
+        <v>35</v>
+      </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="83"/>
-      <c r="B76" s="83"/>
-      <c r="C76" s="83"/>
-      <c r="D76" s="83"/>
-      <c r="E76" s="83"/>
+      <c r="A76" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B76" s="83">
+        <v>100</v>
+      </c>
+      <c r="C76" s="83">
+        <v>5</v>
+      </c>
+      <c r="D76" s="83">
+        <v>95</v>
+      </c>
+      <c r="E76" s="83">
+        <v>105</v>
+      </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="83"/>
-      <c r="B77" s="83"/>
-      <c r="C77" s="83"/>
-      <c r="D77" s="83"/>
-      <c r="E77" s="83"/>
+      <c r="A77" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B77" s="83">
+        <v>240</v>
+      </c>
+      <c r="C77" s="83">
+        <v>5</v>
+      </c>
+      <c r="D77" s="83">
+        <v>235</v>
+      </c>
+      <c r="E77" s="83">
+        <v>245</v>
+      </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="83"/>
-      <c r="B78" s="83"/>
-      <c r="C78" s="83"/>
-      <c r="D78" s="83"/>
-      <c r="E78" s="83"/>
+      <c r="A78" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" s="83">
+        <v>60</v>
+      </c>
+      <c r="C78" s="83">
+        <v>5</v>
+      </c>
+      <c r="D78" s="83">
+        <v>55</v>
+      </c>
+      <c r="E78" s="83">
+        <v>65</v>
+      </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="83"/>
-      <c r="B79" s="83"/>
-      <c r="C79" s="83"/>
-      <c r="D79" s="83"/>
-      <c r="E79" s="83"/>
+      <c r="A79" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B79" s="83">
+        <v>120</v>
+      </c>
+      <c r="C79" s="83">
+        <v>5</v>
+      </c>
+      <c r="D79" s="83">
+        <v>115</v>
+      </c>
+      <c r="E79" s="83">
+        <v>125</v>
+      </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="83"/>
-      <c r="B80" s="83"/>
-      <c r="C80" s="83"/>
-      <c r="D80" s="83"/>
-      <c r="E80" s="83"/>
+      <c r="A80" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B80" s="83">
+        <v>200</v>
+      </c>
+      <c r="C80" s="83">
+        <v>5</v>
+      </c>
+      <c r="D80" s="83">
+        <v>195</v>
+      </c>
+      <c r="E80" s="83">
+        <v>205</v>
+      </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="83"/>
-      <c r="B81" s="83"/>
-      <c r="C81" s="83"/>
-      <c r="D81" s="83"/>
-      <c r="E81" s="83"/>
+      <c r="A81" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B81" s="83">
+        <v>30</v>
+      </c>
+      <c r="C81" s="83">
+        <v>5</v>
+      </c>
+      <c r="D81" s="83">
+        <v>25</v>
+      </c>
+      <c r="E81" s="83">
+        <v>35</v>
+      </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="83"/>
-      <c r="B82" s="83"/>
-      <c r="C82" s="83"/>
-      <c r="D82" s="83"/>
-      <c r="E82" s="83"/>
+      <c r="A82" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B82" s="83">
+        <v>80</v>
+      </c>
+      <c r="C82" s="83">
+        <v>5</v>
+      </c>
+      <c r="D82" s="83">
+        <v>75</v>
+      </c>
+      <c r="E82" s="83">
+        <v>85</v>
+      </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="83"/>
-      <c r="B83" s="83"/>
-      <c r="C83" s="83"/>
-      <c r="D83" s="83"/>
-      <c r="E83" s="83"/>
+      <c r="A83" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B83" s="83">
+        <v>150</v>
+      </c>
+      <c r="C83" s="83">
+        <v>5</v>
+      </c>
+      <c r="D83" s="83">
+        <v>145</v>
+      </c>
+      <c r="E83" s="83">
+        <v>155</v>
+      </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="83"/>
-      <c r="B84" s="83"/>
-      <c r="C84" s="83"/>
-      <c r="D84" s="83"/>
-      <c r="E84" s="83"/>
+      <c r="A84" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B84" s="83">
+        <v>36</v>
+      </c>
+      <c r="C84" s="83">
+        <v>0.8</v>
+      </c>
+      <c r="D84" s="83">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="E84" s="83">
+        <v>36.799999999999997</v>
+      </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="83"/>
-      <c r="B85" s="83"/>
-      <c r="C85" s="83"/>
-      <c r="D85" s="83"/>
-      <c r="E85" s="83"/>
+      <c r="A85" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B85" s="83">
+        <v>38</v>
+      </c>
+      <c r="C85" s="83">
+        <v>0.8</v>
+      </c>
+      <c r="D85" s="83">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="E85" s="83">
+        <v>38.799999999999997</v>
+      </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="83"/>
-      <c r="B86" s="83"/>
-      <c r="C86" s="83"/>
-      <c r="D86" s="83"/>
-      <c r="E86" s="83"/>
+      <c r="A86" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B86" s="83">
+        <v>40</v>
+      </c>
+      <c r="C86" s="83">
+        <v>0.8</v>
+      </c>
+      <c r="D86" s="83">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="E86" s="83">
+        <v>40.799999999999997</v>
+      </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="83"/>
@@ -3757,7 +4063,7 @@
     </row>
     <row r="6" spans="1:16" ht="49.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="55"/>
       <c r="C6" s="55"/>
@@ -3771,7 +4077,7 @@
     </row>
     <row r="8" spans="1:16" s="9" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="57" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="58"/>
       <c r="C8" s="67"/>
